--- a/artfynd/A 32724-2025 artfynd.xlsx
+++ b/artfynd/A 32724-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4318,6 +4318,112 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126379869</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>618614</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7265764</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32724-2025 artfynd.xlsx
+++ b/artfynd/A 32724-2025 artfynd.xlsx
@@ -4323,7 +4323,7 @@
         <v>126379869</v>
       </c>
       <c r="B35" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
